--- a/output/graficos_nacionales/plot_nacional_p_monto_aps_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_p_monto_aps_a_2024.xlsx
@@ -1421,7 +1421,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Monto promedio APS</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>
